--- a/output/pdf_financials_xlsx/BAT.xlsx
+++ b/output/pdf_financials_xlsx/BAT.xlsx
@@ -6171,19 +6171,19 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.420108</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>10.813071</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>11.161022</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>11.334793</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>11.359461</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>0</v>
@@ -7607,10 +7607,10 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>0.170735</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>0.122809</v>
       </c>
       <c r="F118" s="3" t="n">
         <v>0</v>
@@ -21798,7 +21798,11 @@
           <t>Reserve (Note 11)</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -22916,7 +22920,11 @@
           <t>Reserves (Note 12)</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E156" s="5" t="n">
         <v>1.420108</v>
       </c>
@@ -29510,7 +29518,11 @@
           <t>Depreciation on exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -30568,7 +30580,11 @@
           <t>Depreciation on exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BAT.xlsx
+++ b/output/pdf_financials_xlsx/BAT.xlsx
@@ -2891,52 +2891,52 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>4.165965</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>5.628464</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>3.886498</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>15.11332</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>13.14943</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>11.612647</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>6.209353</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>10.178888</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>8.840612</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>7.535159</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>5.148574</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>2.065071</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.224741</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.09887</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.016585</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.035144</v>
       </c>
     </row>
     <row r="35">
@@ -3001,52 +3001,52 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>4.165965</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>5.628464</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>3.886498</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>15.11332</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>13.14943</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.643778</v>
+        <v>12.256425</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>7.05672</v>
+        <v>13.266073</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>2.154681</v>
+        <v>12.333569</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>8.840612</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>7.535159</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>5.148574</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>2.065071</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.224741</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.09887</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.016585</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.035144</v>
       </c>
     </row>
     <row r="37">
@@ -3661,52 +3661,52 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>4.203102</v>
+        <v>0.037137</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>5.753323</v>
+        <v>0.124859</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>4.221775</v>
+        <v>0.335277</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>15.269254</v>
+        <v>0.155934</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>13.275542</v>
+        <v>0.126112</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>10.979263</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>8.117627000000001</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>8.941050000000001</v>
+        <v>0.100438</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>7.587281</v>
+        <v>0.052122</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>5.209735</v>
+        <v>0.061161</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.094012</v>
+        <v>0.028941</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.24254</v>
+        <v>0.017799</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.101635</v>
+        <v>0.002765</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.018366</v>
+        <v>0.001781</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.035354</v>
+        <v>0.00021</v>
       </c>
     </row>
     <row r="49">
@@ -8800,7 +8800,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -20842,7 +20842,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">

--- a/output/pdf_financials_xlsx/BAT.xlsx
+++ b/output/pdf_financials_xlsx/BAT.xlsx
@@ -2481,10 +2481,10 @@
         <v>0.07831200000000001</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.178087</v>
+        <v>0.007352</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.017962</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>0.110851</v>
@@ -2560,10 +2560,10 @@
         <v>-31.544874</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-12.311337</v>
+        <v>-12.482072</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-5.82739</v>
+        <v>-5.809428</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-5.716539</v>
@@ -6581,13 +6581,13 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.007352</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.017962</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.110851</v>
       </c>
       <c r="G100" s="3" t="n">
         <v>0</v>
@@ -29618,7 +29618,11 @@
           <t>Depreciation on property, plant and equipment</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
@@ -30678,7 +30682,11 @@
           <t>Depreciation on property, plant and equipment</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BAT.xlsx
+++ b/output/pdf_financials_xlsx/BAT.xlsx
@@ -4592,16 +4592,16 @@
         <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>1.450639</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.529386</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.472208</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.174403</v>
       </c>
       <c r="G64" s="3" t="n">
         <v>0</v>
@@ -7787,7 +7787,7 @@
         <v>0</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>0</v>
+        <v>-0.44067</v>
       </c>
       <c r="F121" s="3" t="n">
         <v>0</v>
@@ -27716,7 +27716,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -31262,7 +31266,11 @@
           <t>Repurchase of common shares</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
